--- a/fileTemplates/curriculumTemplates/Curriculum_Template 24-25.xlsx
+++ b/fileTemplates/curriculumTemplates/Curriculum_Template 24-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\CAPSTONE-preEnrollment\preEnrollmentV9.3\fileTemplates\curriculumTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0657D48-5177-4219-B89E-1E68AAF75409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94927E4-9AF2-4627-B745-AEE10C8AA352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1st_sem" sheetId="1" r:id="rId1"/>
